--- a/business_forms/012_project_scope_change_request_form--business_forms.xlsx
+++ b/business_forms/012_project_scope_change_request_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Requesting Manager's Job Title</t>
+          <t>Project Scope Change Request Form Data 16</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Affected Project Team Members Department</t>
+          <t>Project Scope Change Request Form Data 23</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Affected Project Team Members Job Title</t>
+          <t>Project Scope Change Request Form Data 24</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'user1',_'label':_'user1',_'value':_'user1'}</t>
+          <t>user1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'User1', 'label': 'User1', 'value': 'User1'}</t>
+          <t>User1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'user2',_'label':_'user2',_'value':_'user2'}</t>
+          <t>user2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'User2', 'label': 'User2', 'value': 'User2'}</t>
+          <t>User2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'user3',_'label':_'user3',_'value':_'user3'}</t>
+          <t>user3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'User3', 'label': 'User3', 'value': 'User3'}</t>
+          <t>User3</t>
         </is>
       </c>
     </row>
